--- a/docs/data/jp/xlsx/6864.xlsx
+++ b/docs/data/jp/xlsx/6864.xlsx
@@ -7941,7 +7941,7 @@
     <row r="97">
       <c r="A97" s="20" t="inlineStr">
         <is>
-          <t>Burden Charge For Development NOI</t>
+          <t>개발 부담금 수입</t>
         </is>
       </c>
       <c r="C97" s="22" t="n">
@@ -7963,7 +7963,7 @@
     <row r="98">
       <c r="A98" s="20" t="inlineStr">
         <is>
-          <t>Sales Of Scraps NOI</t>
+          <t>작업 부스러기 매각 수입</t>
         </is>
       </c>
       <c r="G98" s="22" t="n">
@@ -10924,7 +10924,7 @@
     <row r="155">
       <c r="A155" s="20" t="inlineStr">
         <is>
-          <t>Income From Contribution To Facilities Ope CF</t>
+          <t>수취 설비 부담금</t>
         </is>
       </c>
       <c r="H155" s="22" t="n">
@@ -11951,7 +11951,7 @@
     <row r="180">
       <c r="A180" s="20" t="inlineStr">
         <is>
-          <t>Payments For Extra Retirement Payments And Other Subtotal</t>
+          <t>특별 퇴직금 등 지급액</t>
         </is>
       </c>
       <c r="D180" s="22" t="n">
@@ -13007,7 +13007,7 @@
     <row r="210">
       <c r="A210" s="20" t="inlineStr">
         <is>
-          <t>The Amount Of Payment Of The Dividend To Non Controlling Shareholders Fin CF</t>
+          <t>비지배주주 분배금 지급액</t>
         </is>
       </c>
       <c r="J210" s="22" t="n">
